--- a/jogos_2025-08-31.xlsx
+++ b/jogos_2025-08-31.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="M40" t="n">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="N40" t="n">
-        <v>1.23</v>
+        <v>2.2</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="N43" t="n">
-        <v>2.2</v>
+        <v>1.23</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.63</v>
+        <v>4.3</v>
       </c>
       <c r="M63" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="N63" t="n">
-        <v>5.3</v>
+        <v>1.67</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,22 +10179,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>4.15</v>
+        <v>2.65</v>
       </c>
       <c r="M78" t="n">
-        <v>4.32</v>
+        <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>1.71</v>
+        <v>2.75</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15807,10 +15807,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,22 +16758,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,22 +17145,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17865,10 +17865,10 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA135" t="n">
         <v>0</v>
@@ -17919,22 +17919,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18471,13 +18471,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -18516,10 +18516,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,22 +19854,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,22 +19983,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20277,13 +20277,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20316,10 +20316,10 @@
         <v>0</v>
       </c>
       <c r="Y154" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z154" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA154" t="n">
         <v>0</v>
@@ -20370,22 +20370,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,22 +20499,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20793,13 +20793,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -20832,10 +20832,10 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA158" t="n">
         <v>0</v>
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,22 +21273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,22 +21402,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22083,13 +22083,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="M168" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N168" t="n">
-        <v>1.97</v>
+        <v>2.65</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="Y168" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z168" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AA168" t="n">
         <v>0</v>
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22212,13 +22212,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22251,10 +22251,10 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA169" t="n">
         <v>0</v>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,22 +22563,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23502,13 +23502,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M179" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="N179" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -23547,10 +23547,10 @@
         <v>2.62</v>
       </c>
       <c r="AA179" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23631,13 +23631,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="M180" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N180" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -23670,10 +23670,10 @@
         <v>0</v>
       </c>
       <c r="Y180" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z180" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA180" t="n">
         <v>0</v>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23889,13 +23889,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -23928,10 +23928,10 @@
         <v>0</v>
       </c>
       <c r="Y182" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z182" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA182" t="n">
         <v>0</v>
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24147,13 +24147,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24240,22 +24240,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24885,22 +24885,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,22 +25014,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,22 +25143,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26082,13 +26082,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26121,10 +26121,10 @@
         <v>0</v>
       </c>
       <c r="Y199" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z199" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA199" t="n">
         <v>0</v>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26211,13 +26211,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -26250,10 +26250,10 @@
         <v>0</v>
       </c>
       <c r="Y200" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z200" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA200" t="n">
         <v>0</v>
@@ -26433,22 +26433,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,22 +26820,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,22 +27207,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,22 +27594,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,22 +27981,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,22 +28110,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28146,13 +28146,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z215" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA215" t="n">
         <v>0</v>
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28314,10 +28314,10 @@
         <v>0</v>
       </c>
       <c r="Y216" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z216" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA216" t="n">
         <v>0</v>
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,22 +28497,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28626,22 +28626,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29178,13 +29178,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M223" t="n">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="N223" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29217,10 +29217,10 @@
         <v>0</v>
       </c>
       <c r="Y223" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z223" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AA223" t="n">
         <v>0</v>
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29307,13 +29307,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -29346,10 +29346,10 @@
         <v>0</v>
       </c>
       <c r="Y224" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA224" t="n">
         <v>0</v>
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,22 +29916,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30174,22 +30174,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="M234" t="n">
         <v>3.15</v>
       </c>
       <c r="N234" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="M235" t="n">
         <v>3.15</v>
       </c>
       <c r="N235" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z239" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,22 +31464,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,22 +31593,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31629,13 +31629,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -31668,10 +31668,10 @@
         <v>0</v>
       </c>
       <c r="Y242" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z242" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA242" t="n">
         <v>0</v>
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31758,13 +31758,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="M243" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="N243" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -31797,10 +31797,10 @@
         <v>0</v>
       </c>
       <c r="Y243" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z243" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AA243" t="n">
         <v>0</v>
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31887,13 +31887,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="M244" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="N244" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -31926,10 +31926,10 @@
         <v>0</v>
       </c>
       <c r="Y244" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="Z244" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AA244" t="n">
         <v>0</v>
@@ -31980,22 +31980,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32274,13 +32274,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -32313,10 +32313,10 @@
         <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z247" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA247" t="n">
         <v>0</v>
@@ -32367,7 +32367,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32403,13 +32403,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -32442,10 +32442,10 @@
         <v>0</v>
       </c>
       <c r="Y248" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z248" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA248" t="n">
         <v>0</v>
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32532,13 +32532,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>1.39</v>
+        <v>2.25</v>
       </c>
       <c r="M249" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="N249" t="n">
-        <v>7.5</v>
+        <v>3.25</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -32571,10 +32571,10 @@
         <v>0</v>
       </c>
       <c r="Y249" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="Z249" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AA249" t="n">
         <v>0</v>
@@ -32625,22 +32625,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32883,22 +32883,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33012,22 +33012,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,22 +33141,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33270,22 +33270,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,22 +33399,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,22 +33786,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35241,13 +35241,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="M270" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N270" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -35274,16 +35274,16 @@
         <v>0</v>
       </c>
       <c r="W270" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X270" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y270" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="Z270" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AA270" t="n">
         <v>0</v>
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35370,13 +35370,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="M271" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N271" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -35403,16 +35403,16 @@
         <v>0</v>
       </c>
       <c r="W271" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X271" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y271" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="Z271" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AA271" t="n">
         <v>0</v>
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35860,12 +35860,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36015,13 +36015,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -36054,10 +36054,10 @@
         <v>0</v>
       </c>
       <c r="Y276" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Z276" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA276" t="n">
         <v>0</v>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36273,13 +36273,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N278" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -36312,10 +36312,10 @@
         <v>0</v>
       </c>
       <c r="Y278" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Z278" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA278" t="n">
         <v>0</v>

--- a/jogos_2025-08-31.xlsx
+++ b/jogos_2025-08-31.xlsx
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4922,17 +4922,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5358,10 +5358,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5487,10 +5487,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="M64" t="n">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="N64" t="n">
-        <v>2.35</v>
+        <v>1.68</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="M127" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N127" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,22 +16887,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17865,10 +17865,10 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z135" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA135" t="n">
         <v>0</v>
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22083,13 +22083,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="M168" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N168" t="n">
-        <v>3.45</v>
+        <v>2.07</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="Y168" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z168" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA168" t="n">
         <v>0</v>
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22212,13 +22212,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22251,10 +22251,10 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z169" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA169" t="n">
         <v>0</v>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22341,13 +22341,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.37</v>
+        <v>1.79</v>
       </c>
       <c r="M173" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="N173" t="n">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,16 +22767,16 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z173" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA173" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB173" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC173" t="n">
         <v>0</v>
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23115,13 +23115,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.79</v>
+        <v>1.37</v>
       </c>
       <c r="M176" t="n">
-        <v>3.55</v>
+        <v>5.3</v>
       </c>
       <c r="N176" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23154,16 +23154,16 @@
         <v>0</v>
       </c>
       <c r="Y176" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z176" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA176" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB176" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,22 +24111,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,22 +24498,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,22 +24627,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,22 +24885,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25050,13 +25050,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25089,10 +25089,10 @@
         <v>0</v>
       </c>
       <c r="Y191" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z191" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA191" t="n">
         <v>0</v>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25218,10 +25218,10 @@
         <v>0</v>
       </c>
       <c r="Y192" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Z192" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA192" t="n">
         <v>0</v>
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25308,13 +25308,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25347,10 +25347,10 @@
         <v>0</v>
       </c>
       <c r="Y193" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z193" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA193" t="n">
         <v>0</v>
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25437,13 +25437,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -25476,10 +25476,10 @@
         <v>0</v>
       </c>
       <c r="Y194" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z194" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA194" t="n">
         <v>0</v>
@@ -25788,22 +25788,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,22 +26046,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,22 +26175,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,22 +26433,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26727,13 +26727,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -26766,10 +26766,10 @@
         <v>0</v>
       </c>
       <c r="Y204" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z204" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA204" t="n">
         <v>0</v>
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27114,13 +27114,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27153,10 +27153,10 @@
         <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z207" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA207" t="n">
         <v>0</v>
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,22 +27852,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,22 +27981,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28239,22 +28239,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28368,22 +28368,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28572,10 +28572,10 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z218" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA218" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -28701,10 +28701,10 @@
         <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z219" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA219" t="n">
         <v>0</v>
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,10 +28959,10 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z221" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA221" t="n">
         <v>0</v>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29565,13 +29565,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -29604,10 +29604,10 @@
         <v>0</v>
       </c>
       <c r="Y226" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z226" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA226" t="n">
         <v>0</v>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29694,13 +29694,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -29733,10 +29733,10 @@
         <v>0</v>
       </c>
       <c r="Y227" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z227" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA227" t="n">
         <v>0</v>
@@ -29916,22 +29916,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,22 +30045,22 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30948,22 +30948,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31335,22 +31335,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31980,22 +31980,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,22 +32367,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33012,22 +33012,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,22 +33141,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G273" t="n">

--- a/jogos_2025-08-31.xlsx
+++ b/jogos_2025-08-31.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK292"/>
+  <dimension ref="A1:AK294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Sydney II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4922,17 +4922,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5487,10 +5487,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="M43" t="n">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>1.23</v>
+        <v>2.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45900.35416666666</v>
+        <v>45900.33333333334</v>
       </c>
     </row>
     <row r="45">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45900.35763888889</v>
+        <v>45900.35416666666</v>
       </c>
     </row>
     <row r="50">
@@ -6949,27 +6949,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45900.375</v>
+        <v>45900.35763888889</v>
       </c>
     </row>
     <row r="52">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8497,27 +8497,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45900.39583333334</v>
+        <v>45900.375</v>
       </c>
     </row>
     <row r="64">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,22 +8889,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.63</v>
+        <v>2.8</v>
       </c>
       <c r="M68" t="n">
-        <v>3.98</v>
+        <v>3.7</v>
       </c>
       <c r="N68" t="n">
-        <v>5.3</v>
+        <v>2.35</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9271,12 +9271,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="M69" t="n">
-        <v>3.45</v>
+        <v>3.98</v>
       </c>
       <c r="N69" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AK69" s="3" t="n">
-        <v>45900.40625</v>
+        <v>45900.39583333334</v>
       </c>
     </row>
     <row r="70">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>4.15</v>
+        <v>1.85</v>
       </c>
       <c r="M70" t="n">
-        <v>4.32</v>
+        <v>3.45</v>
       </c>
       <c r="N70" t="n">
-        <v>1.71</v>
+        <v>4.6</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45900.41666666666</v>
+        <v>45900.40625</v>
       </c>
     </row>
     <row r="71">
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,22 +10308,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10819,12 +10819,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.25</v>
+        <v>4.15</v>
       </c>
       <c r="M81" t="n">
-        <v>3.6</v>
+        <v>4.32</v>
       </c>
       <c r="N81" t="n">
-        <v>3.05</v>
+        <v>1.71</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.13</v>
+        <v>2.37</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="AK81" s="3" t="n">
-        <v>45900.4375</v>
+        <v>45900.41666666666</v>
       </c>
     </row>
     <row r="82">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11464,12 +11464,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45900.45833333334</v>
+        <v>45900.4375</v>
       </c>
     </row>
     <row r="87">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14044,12 +14044,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="AK106" s="3" t="n">
-        <v>45900.47916666666</v>
+        <v>45900.45833333334</v>
       </c>
     </row>
     <row r="107">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45900.48958333334</v>
+        <v>45900.47916666666</v>
       </c>
     </row>
     <row r="114">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45900.5</v>
+        <v>45900.48958333334</v>
       </c>
     </row>
     <row r="116">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,22 +16242,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="M126" t="n">
         <v>3.45</v>
       </c>
       <c r="N126" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,22 +16887,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.77</v>
+        <v>3.7</v>
       </c>
       <c r="M134" t="n">
         <v>3.6</v>
       </c>
       <c r="N134" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z134" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,22 +18435,22 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,22 +19983,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,22 +20112,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,22 +20241,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,22 +20499,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,22 +20628,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,22 +20757,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,22 +20886,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21526,12 +21526,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21646,7 +21646,7 @@
         <v>0</v>
       </c>
       <c r="AK164" s="3" t="n">
-        <v>45900.51041666666</v>
+        <v>45900.5</v>
       </c>
     </row>
     <row r="165">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21913,27 +21913,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22033,7 +22033,7 @@
         <v>0</v>
       </c>
       <c r="AK167" s="3" t="n">
-        <v>45900.51736111111</v>
+        <v>45900.51041666666</v>
       </c>
     </row>
     <row r="168">
@@ -22042,27 +22042,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22083,13 +22083,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
         <v>0</v>
       </c>
       <c r="AK168" s="3" t="n">
-        <v>45900.52083333334</v>
+        <v>45900.51736111111</v>
       </c>
     </row>
     <row r="169">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22212,13 +22212,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22251,10 +22251,10 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z169" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA169" t="n">
         <v>0</v>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22341,13 +22341,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22470,13 +22470,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22857,13 +22857,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -22896,16 +22896,16 @@
         <v>0</v>
       </c>
       <c r="Y174" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z174" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA174" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23115,13 +23115,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="M176" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="N176" t="n">
-        <v>7.6</v>
+        <v>3.45</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23154,16 +23154,16 @@
         <v>0</v>
       </c>
       <c r="Y176" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="Z176" t="n">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="AA176" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB176" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -23203,12 +23203,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23323,7 +23323,7 @@
         <v>0</v>
       </c>
       <c r="AK177" s="3" t="n">
-        <v>45900.54166666666</v>
+        <v>45900.52083333334</v>
       </c>
     </row>
     <row r="178">
@@ -23337,22 +23337,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,22 +24111,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24498,22 +24498,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,22 +24756,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25009,27 +25009,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25129,7 +25129,7 @@
         <v>0</v>
       </c>
       <c r="AK191" s="3" t="n">
-        <v>45900.55208333334</v>
+        <v>45900.54166666666</v>
       </c>
     </row>
     <row r="192">
@@ -25138,12 +25138,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25218,10 +25218,10 @@
         <v>0</v>
       </c>
       <c r="Y192" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z192" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA192" t="n">
         <v>0</v>
@@ -25258,7 +25258,7 @@
         <v>0</v>
       </c>
       <c r="AK192" s="3" t="n">
-        <v>45900.55208333334</v>
+        <v>45900.54166666666</v>
       </c>
     </row>
     <row r="193">
@@ -25267,12 +25267,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25308,13 +25308,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25347,10 +25347,10 @@
         <v>0</v>
       </c>
       <c r="Y193" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z193" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA193" t="n">
         <v>0</v>
@@ -25387,7 +25387,7 @@
         <v>0</v>
       </c>
       <c r="AK193" s="3" t="n">
-        <v>45900.5625</v>
+        <v>45900.55208333334</v>
       </c>
     </row>
     <row r="194">
@@ -25396,12 +25396,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25437,13 +25437,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -25476,10 +25476,10 @@
         <v>0</v>
       </c>
       <c r="Y194" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Z194" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA194" t="n">
         <v>0</v>
@@ -25516,7 +25516,7 @@
         <v>0</v>
       </c>
       <c r="AK194" s="3" t="n">
-        <v>45900.5625</v>
+        <v>45900.55208333334</v>
       </c>
     </row>
     <row r="195">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25695,13 +25695,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -25734,10 +25734,10 @@
         <v>0</v>
       </c>
       <c r="Y196" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z196" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA196" t="n">
         <v>0</v>
@@ -25783,27 +25783,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25824,13 +25824,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -25863,10 +25863,10 @@
         <v>0</v>
       </c>
       <c r="Y197" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z197" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA197" t="n">
         <v>0</v>
@@ -25903,7 +25903,7 @@
         <v>0</v>
       </c>
       <c r="AK197" s="3" t="n">
-        <v>45900.58333333334</v>
+        <v>45900.5625</v>
       </c>
     </row>
     <row r="198">
@@ -25912,12 +25912,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -25953,13 +25953,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -25992,10 +25992,10 @@
         <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z198" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA198" t="n">
         <v>0</v>
@@ -26032,7 +26032,7 @@
         <v>0</v>
       </c>
       <c r="AK198" s="3" t="n">
-        <v>45900.58333333334</v>
+        <v>45900.5625</v>
       </c>
     </row>
     <row r="199">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,22 +26433,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,22 +26691,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26727,13 +26727,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -26766,10 +26766,10 @@
         <v>0</v>
       </c>
       <c r="Y204" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z204" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA204" t="n">
         <v>0</v>
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,22 +26949,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,22 +27852,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,22 +27981,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28105,12 +28105,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28146,13 +28146,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z215" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA215" t="n">
         <v>0</v>
@@ -28225,7 +28225,7 @@
         <v>0</v>
       </c>
       <c r="AK215" s="3" t="n">
-        <v>45900.59375</v>
+        <v>45900.58333333334</v>
       </c>
     </row>
     <row r="216">
@@ -28234,27 +28234,27 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28354,7 +28354,7 @@
         <v>0</v>
       </c>
       <c r="AK216" s="3" t="n">
-        <v>45900.59375</v>
+        <v>45900.58333333334</v>
       </c>
     </row>
     <row r="217">
@@ -28492,7 +28492,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28612,7 +28612,7 @@
         <v>0</v>
       </c>
       <c r="AK218" s="3" t="n">
-        <v>45900.60416666666</v>
+        <v>45900.59375</v>
       </c>
     </row>
     <row r="219">
@@ -28621,27 +28621,27 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -28701,10 +28701,10 @@
         <v>0</v>
       </c>
       <c r="Y219" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z219" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA219" t="n">
         <v>0</v>
@@ -28741,7 +28741,7 @@
         <v>0</v>
       </c>
       <c r="AK219" s="3" t="n">
-        <v>45900.60416666666</v>
+        <v>45900.59375</v>
       </c>
     </row>
     <row r="220">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,10 +28959,10 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA221" t="n">
         <v>0</v>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29395,12 +29395,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29436,13 +29436,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -29475,10 +29475,10 @@
         <v>0</v>
       </c>
       <c r="Y225" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z225" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA225" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
         <v>0</v>
       </c>
       <c r="AK225" s="3" t="n">
-        <v>45900.625</v>
+        <v>45900.60416666666</v>
       </c>
     </row>
     <row r="226">
@@ -29524,12 +29524,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29565,13 +29565,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="M226" t="n">
-        <v>4.2</v>
+        <v>3.24</v>
       </c>
       <c r="N226" t="n">
-        <v>7.6</v>
+        <v>2.89</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -29604,10 +29604,10 @@
         <v>0</v>
       </c>
       <c r="Y226" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="Z226" t="n">
-        <v>1.97</v>
+        <v>1.66</v>
       </c>
       <c r="AA226" t="n">
         <v>0</v>
@@ -29644,7 +29644,7 @@
         <v>0</v>
       </c>
       <c r="AK226" s="3" t="n">
-        <v>45900.625</v>
+        <v>45900.60416666666</v>
       </c>
     </row>
     <row r="227">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29916,22 +29916,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,22 +30174,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30298,12 +30298,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30339,13 +30339,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>2.55</v>
+        <v>1.36</v>
       </c>
       <c r="M232" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="N232" t="n">
-        <v>2.55</v>
+        <v>7.6</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -30378,10 +30378,10 @@
         <v>0</v>
       </c>
       <c r="Y232" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z232" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA232" t="n">
         <v>0</v>
@@ -30418,7 +30418,7 @@
         <v>0</v>
       </c>
       <c r="AK232" s="3" t="n">
-        <v>45900.63541666666</v>
+        <v>45900.625</v>
       </c>
     </row>
     <row r="233">
@@ -30427,12 +30427,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30468,13 +30468,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N233" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -30547,7 +30547,7 @@
         <v>0</v>
       </c>
       <c r="AK233" s="3" t="n">
-        <v>45900.63541666666</v>
+        <v>45900.625</v>
       </c>
     </row>
     <row r="234">
@@ -30556,12 +30556,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30676,7 +30676,7 @@
         <v>0</v>
       </c>
       <c r="AK234" s="3" t="n">
-        <v>45900.64583333334</v>
+        <v>45900.63541666666</v>
       </c>
     </row>
     <row r="235">
@@ -30685,27 +30685,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -30805,7 +30805,7 @@
         <v>0</v>
       </c>
       <c r="AK235" s="3" t="n">
-        <v>45900.64583333334</v>
+        <v>45900.63541666666</v>
       </c>
     </row>
     <row r="236">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30855,13 +30855,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -30894,10 +30894,10 @@
         <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z236" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA236" t="n">
         <v>0</v>
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31335,22 +31335,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M240" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31410,10 +31410,10 @@
         <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z240" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA240" t="n">
         <v>0</v>
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31500,13 +31500,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -31588,12 +31588,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31629,13 +31629,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -31668,10 +31668,10 @@
         <v>0</v>
       </c>
       <c r="Y242" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z242" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA242" t="n">
         <v>0</v>
@@ -31708,7 +31708,7 @@
         <v>0</v>
       </c>
       <c r="AK242" s="3" t="n">
-        <v>45900.65625</v>
+        <v>45900.64583333334</v>
       </c>
     </row>
     <row r="243">
@@ -31717,27 +31717,27 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31758,13 +31758,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N243" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -31797,10 +31797,10 @@
         <v>0</v>
       </c>
       <c r="Y243" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z243" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA243" t="n">
         <v>0</v>
@@ -31837,7 +31837,7 @@
         <v>0</v>
       </c>
       <c r="AK243" s="3" t="n">
-        <v>45900.65625</v>
+        <v>45900.64583333334</v>
       </c>
     </row>
     <row r="244">
@@ -31975,12 +31975,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32016,13 +32016,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32055,10 +32055,10 @@
         <v>0</v>
       </c>
       <c r="Y245" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z245" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA245" t="n">
         <v>0</v>
@@ -32095,7 +32095,7 @@
         <v>0</v>
       </c>
       <c r="AK245" s="3" t="n">
-        <v>45900.66666666666</v>
+        <v>45900.65625</v>
       </c>
     </row>
     <row r="246">
@@ -32104,12 +32104,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32145,13 +32145,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -32184,10 +32184,10 @@
         <v>0</v>
       </c>
       <c r="Y246" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z246" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA246" t="n">
         <v>0</v>
@@ -32224,7 +32224,7 @@
         <v>0</v>
       </c>
       <c r="AK246" s="3" t="n">
-        <v>45900.66666666666</v>
+        <v>45900.65625</v>
       </c>
     </row>
     <row r="247">
@@ -32238,22 +32238,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,22 +32496,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,22 +32625,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32883,22 +32883,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33270,22 +33270,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33435,13 +33435,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N256" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -33474,10 +33474,10 @@
         <v>0</v>
       </c>
       <c r="Y256" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z256" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA256" t="n">
         <v>0</v>
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33915,22 +33915,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34080,13 +34080,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34125,10 +34125,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB261" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34209,13 +34209,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -34254,10 +34254,10 @@
         <v>0</v>
       </c>
       <c r="AA262" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB262" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC262" t="n">
         <v>0</v>
@@ -34302,22 +34302,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34377,10 +34377,10 @@
         <v>0</v>
       </c>
       <c r="Y263" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z263" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA263" t="n">
         <v>0</v>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34560,22 +34560,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34596,13 +34596,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N265" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -34635,10 +34635,10 @@
         <v>0</v>
       </c>
       <c r="Y265" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z265" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA265" t="n">
         <v>0</v>
@@ -34689,22 +34689,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34725,13 +34725,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M266" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -34764,10 +34764,10 @@
         <v>0</v>
       </c>
       <c r="Y266" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z266" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA266" t="n">
         <v>0</v>
@@ -34813,27 +34813,27 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34933,7 +34933,7 @@
         <v>0</v>
       </c>
       <c r="AK267" s="3" t="n">
-        <v>45900.67708333334</v>
+        <v>45900.66666666666</v>
       </c>
     </row>
     <row r="268">
@@ -34942,12 +34942,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35062,7 +35062,7 @@
         <v>0</v>
       </c>
       <c r="AK268" s="3" t="n">
-        <v>45900.67708333334</v>
+        <v>45900.66666666666</v>
       </c>
     </row>
     <row r="269">
@@ -35071,27 +35071,27 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35191,7 +35191,7 @@
         <v>0</v>
       </c>
       <c r="AK269" s="3" t="n">
-        <v>45900.6875</v>
+        <v>45900.67708333334</v>
       </c>
     </row>
     <row r="270">
@@ -35200,27 +35200,27 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35320,7 +35320,7 @@
         <v>0</v>
       </c>
       <c r="AK270" s="3" t="n">
-        <v>45900.6875</v>
+        <v>45900.67708333334</v>
       </c>
     </row>
     <row r="271">
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35716,27 +35716,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35836,7 +35836,7 @@
         <v>0</v>
       </c>
       <c r="AK274" s="3" t="n">
-        <v>45900.70138888889</v>
+        <v>45900.6875</v>
       </c>
     </row>
     <row r="275">
@@ -35845,27 +35845,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35965,7 +35965,7 @@
         <v>0</v>
       </c>
       <c r="AK275" s="3" t="n">
-        <v>45900.70833333334</v>
+        <v>45900.6875</v>
       </c>
     </row>
     <row r="276">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36015,13 +36015,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N276" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -36054,10 +36054,10 @@
         <v>0</v>
       </c>
       <c r="Y276" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z276" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA276" t="n">
         <v>0</v>
@@ -36094,7 +36094,7 @@
         <v>0</v>
       </c>
       <c r="AK276" s="3" t="n">
-        <v>45900.77083333334</v>
+        <v>45900.70138888889</v>
       </c>
     </row>
     <row r="277">
@@ -36103,12 +36103,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36144,13 +36144,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N277" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -36177,16 +36177,16 @@
         <v>0</v>
       </c>
       <c r="W277" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X277" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y277" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Z277" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -36223,7 +36223,7 @@
         <v>0</v>
       </c>
       <c r="AK277" s="3" t="n">
-        <v>45900.77083333334</v>
+        <v>45900.70833333334</v>
       </c>
     </row>
     <row r="278">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36273,13 +36273,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="M278" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N278" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -36306,16 +36306,16 @@
         <v>0</v>
       </c>
       <c r="W278" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X278" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y278" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Z278" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AA278" t="n">
         <v>0</v>
@@ -36361,12 +36361,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36402,13 +36402,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N279" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -36435,16 +36435,16 @@
         <v>0</v>
       </c>
       <c r="W279" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X279" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y279" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Z279" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA279" t="n">
         <v>0</v>
@@ -36481,7 +36481,7 @@
         <v>0</v>
       </c>
       <c r="AK279" s="3" t="n">
-        <v>45900.8125</v>
+        <v>45900.77083333334</v>
       </c>
     </row>
     <row r="280">
@@ -36490,12 +36490,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36531,13 +36531,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -36564,16 +36564,16 @@
         <v>0</v>
       </c>
       <c r="W280" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X280" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y280" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Z280" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA280" t="n">
         <v>0</v>
@@ -36610,7 +36610,7 @@
         <v>0</v>
       </c>
       <c r="AK280" s="3" t="n">
-        <v>45900.83333333334</v>
+        <v>45900.77083333334</v>
       </c>
     </row>
     <row r="281">
@@ -36619,12 +36619,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -36634,12 +36634,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36739,7 +36739,7 @@
         <v>0</v>
       </c>
       <c r="AK281" s="3" t="n">
-        <v>45900.83333333334</v>
+        <v>45900.8125</v>
       </c>
     </row>
     <row r="282">
@@ -36877,7 +36877,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -36997,7 +36997,7 @@
         <v>0</v>
       </c>
       <c r="AK283" s="3" t="n">
-        <v>45900.85416666666</v>
+        <v>45900.83333333334</v>
       </c>
     </row>
     <row r="284">
@@ -37006,12 +37006,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37047,13 +37047,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37086,10 +37086,10 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z284" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA284" t="n">
         <v>0</v>
@@ -37126,7 +37126,7 @@
         <v>0</v>
       </c>
       <c r="AK284" s="3" t="n">
-        <v>45900.85416666666</v>
+        <v>45900.83333333334</v>
       </c>
     </row>
     <row r="285">
@@ -37264,12 +37264,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -37279,12 +37279,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -37384,7 +37384,7 @@
         <v>0</v>
       </c>
       <c r="AK286" s="3" t="n">
-        <v>45900.875</v>
+        <v>45900.85416666666</v>
       </c>
     </row>
     <row r="287">
@@ -37393,12 +37393,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37434,13 +37434,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M287" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N287" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -37473,10 +37473,10 @@
         <v>0</v>
       </c>
       <c r="Y287" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z287" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA287" t="n">
         <v>0</v>
@@ -37513,7 +37513,7 @@
         <v>0</v>
       </c>
       <c r="AK287" s="3" t="n">
-        <v>45900.875</v>
+        <v>45900.85416666666</v>
       </c>
     </row>
     <row r="288">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37651,12 +37651,12 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37771,7 +37771,7 @@
         <v>0</v>
       </c>
       <c r="AK289" s="3" t="n">
-        <v>45900.88541666666</v>
+        <v>45900.875</v>
       </c>
     </row>
     <row r="290">
@@ -37780,12 +37780,12 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -37795,12 +37795,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37900,7 +37900,7 @@
         <v>0</v>
       </c>
       <c r="AK290" s="3" t="n">
-        <v>45900.9375</v>
+        <v>45900.875</v>
       </c>
     </row>
     <row r="291">
@@ -37909,12 +37909,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -37924,12 +37924,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38029,7 +38029,7 @@
         <v>0</v>
       </c>
       <c r="AK291" s="3" t="n">
-        <v>45900.95833333334</v>
+        <v>45900.88541666666</v>
       </c>
     </row>
     <row r="292">
@@ -38038,126 +38038,384 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Real Monarchs</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Tacoma Defiance</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" t="n">
+        <v>0</v>
+      </c>
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="n">
+        <v>0</v>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L292" t="n">
+        <v>0</v>
+      </c>
+      <c r="M292" t="n">
+        <v>0</v>
+      </c>
+      <c r="N292" t="n">
+        <v>0</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
+      <c r="P292" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>0</v>
+      </c>
+      <c r="R292" t="n">
+        <v>0</v>
+      </c>
+      <c r="S292" t="n">
+        <v>0</v>
+      </c>
+      <c r="T292" t="n">
+        <v>0</v>
+      </c>
+      <c r="U292" t="n">
+        <v>0</v>
+      </c>
+      <c r="V292" t="n">
+        <v>0</v>
+      </c>
+      <c r="W292" t="n">
+        <v>0</v>
+      </c>
+      <c r="X292" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y292" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF292" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK292" s="3" t="n">
+        <v>45900.9375</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>LA Galaxy II</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>North Texas</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" t="n">
+        <v>0</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L293" t="n">
+        <v>0</v>
+      </c>
+      <c r="M293" t="n">
+        <v>0</v>
+      </c>
+      <c r="N293" t="n">
+        <v>0</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0</v>
+      </c>
+      <c r="P293" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>0</v>
+      </c>
+      <c r="R293" t="n">
+        <v>0</v>
+      </c>
+      <c r="S293" t="n">
+        <v>0</v>
+      </c>
+      <c r="T293" t="n">
+        <v>0</v>
+      </c>
+      <c r="U293" t="n">
+        <v>0</v>
+      </c>
+      <c r="V293" t="n">
+        <v>0</v>
+      </c>
+      <c r="W293" t="n">
+        <v>0</v>
+      </c>
+      <c r="X293" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y293" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF293" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK293" s="3" t="n">
+        <v>45900.95833333334</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
+      <c r="C294" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr">
+      <c r="D294" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr">
+      <c r="E294" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr">
+      <c r="F294" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="G292" t="n">
-        <v>0</v>
-      </c>
-      <c r="H292" t="n">
-        <v>0</v>
-      </c>
-      <c r="I292" t="n">
-        <v>0</v>
-      </c>
-      <c r="J292" t="n">
-        <v>0</v>
-      </c>
-      <c r="K292" t="inlineStr">
+      <c r="G294" t="n">
+        <v>0</v>
+      </c>
+      <c r="H294" t="n">
+        <v>0</v>
+      </c>
+      <c r="I294" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L292" t="n">
+      <c r="L294" t="n">
         <v>1.71</v>
       </c>
-      <c r="M292" t="n">
+      <c r="M294" t="n">
         <v>4.2</v>
       </c>
-      <c r="N292" t="n">
+      <c r="N294" t="n">
         <v>3.85</v>
       </c>
-      <c r="O292" t="n">
-        <v>0</v>
-      </c>
-      <c r="P292" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
-      <c r="R292" t="n">
-        <v>0</v>
-      </c>
-      <c r="S292" t="n">
-        <v>0</v>
-      </c>
-      <c r="T292" t="n">
-        <v>0</v>
-      </c>
-      <c r="U292" t="n">
-        <v>0</v>
-      </c>
-      <c r="V292" t="n">
-        <v>0</v>
-      </c>
-      <c r="W292" t="n">
-        <v>0</v>
-      </c>
-      <c r="X292" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y292" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z292" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA292" t="n">
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
+      <c r="P294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>0</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="n">
+        <v>0</v>
+      </c>
+      <c r="T294" t="n">
+        <v>0</v>
+      </c>
+      <c r="U294" t="n">
+        <v>0</v>
+      </c>
+      <c r="V294" t="n">
+        <v>0</v>
+      </c>
+      <c r="W294" t="n">
+        <v>0</v>
+      </c>
+      <c r="X294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA294" t="n">
         <v>2.2</v>
       </c>
-      <c r="AB292" t="n">
+      <c r="AB294" t="n">
         <v>1.61</v>
       </c>
-      <c r="AC292" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD292" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE292" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF292" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG292" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH292" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI292" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ292" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK292" s="3" t="n">
+      <c r="AC294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE294" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF294" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK294" s="3" t="n">
         <v>45900.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-31.xlsx
+++ b/jogos_2025-08-31.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK294"/>
+  <dimension ref="A1:AK293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="N43" t="n">
-        <v>2.2</v>
+        <v>1.23</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.63</v>
+        <v>4.7</v>
       </c>
       <c r="M69" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="N69" t="n">
-        <v>5.3</v>
+        <v>1.68</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.65</v>
+        <v>1.82</v>
       </c>
       <c r="M71" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>2.75</v>
+        <v>4.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="M72" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="N72" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,22 +10179,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,22 +10308,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="M78" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,22 +11727,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16452,10 +16452,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.2</v>
+        <v>1.77</v>
       </c>
       <c r="M131" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="N131" t="n">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,16 +17349,16 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA131" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.77</v>
+        <v>3.75</v>
       </c>
       <c r="M132" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N132" t="n">
-        <v>4.8</v>
+        <v>2.02</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z132" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>2</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="M133" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N133" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Z133" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17697,13 +17697,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -17736,10 +17736,10 @@
         <v>0</v>
       </c>
       <c r="Y134" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z134" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA134" t="n">
         <v>0</v>
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,22 +18048,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,22 +18564,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,22 +18693,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -18897,10 +18897,10 @@
         <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA143" t="n">
         <v>0</v>
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,22 +19209,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,22 +20112,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,22 +20757,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,22 +20886,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22212,13 +22212,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22341,13 +22341,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22470,13 +22470,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="M171" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N171" t="n">
-        <v>2.07</v>
+        <v>3.45</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -22509,10 +22509,10 @@
         <v>0</v>
       </c>
       <c r="Y171" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z171" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA171" t="n">
         <v>0</v>
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22599,13 +22599,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -22638,16 +22638,16 @@
         <v>0</v>
       </c>
       <c r="Y172" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z172" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA172" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22857,13 +22857,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -22896,16 +22896,16 @@
         <v>0</v>
       </c>
       <c r="Y174" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z174" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23025,10 +23025,10 @@
         <v>0</v>
       </c>
       <c r="Y175" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z175" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA175" t="n">
         <v>0</v>
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23115,13 +23115,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23154,10 +23154,10 @@
         <v>0</v>
       </c>
       <c r="Y176" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z176" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA176" t="n">
         <v>0</v>
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,22 +23337,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,22 +23595,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,22 +23724,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
+          <t>Harju Jalgpallikool</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
           <t>Tammeka</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,22 +25014,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25308,13 +25308,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25347,10 +25347,10 @@
         <v>0</v>
       </c>
       <c r="Y193" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Z193" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA193" t="n">
         <v>0</v>
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25437,13 +25437,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -25476,10 +25476,10 @@
         <v>0</v>
       </c>
       <c r="Y194" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z194" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA194" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25695,13 +25695,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -25734,10 +25734,10 @@
         <v>0</v>
       </c>
       <c r="Y196" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z196" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA196" t="n">
         <v>0</v>
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25824,13 +25824,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="M197" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N197" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -25863,10 +25863,10 @@
         <v>0</v>
       </c>
       <c r="Y197" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z197" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AA197" t="n">
         <v>0</v>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -25953,13 +25953,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -25992,10 +25992,10 @@
         <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z198" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA198" t="n">
         <v>0</v>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,22 +26175,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,22 +26562,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,22 +26691,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,22 +26820,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,22 +26949,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,22 +27465,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27630,13 +27630,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -27669,10 +27669,10 @@
         <v>0</v>
       </c>
       <c r="Y211" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z211" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA211" t="n">
         <v>0</v>
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28146,13 +28146,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28185,10 +28185,10 @@
         <v>0</v>
       </c>
       <c r="Y215" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z215" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA215" t="n">
         <v>0</v>
@@ -28497,22 +28497,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28626,22 +28626,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,10 +28959,10 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z221" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA221" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29178,13 +29178,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29217,10 +29217,10 @@
         <v>0</v>
       </c>
       <c r="Y223" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z223" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA223" t="n">
         <v>0</v>
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29436,13 +29436,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -29475,10 +29475,10 @@
         <v>0</v>
       </c>
       <c r="Y225" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z225" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA225" t="n">
         <v>0</v>
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29565,13 +29565,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -29604,10 +29604,10 @@
         <v>0</v>
       </c>
       <c r="Y226" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z226" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA226" t="n">
         <v>0</v>
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z230" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30174,22 +30174,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30339,13 +30339,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -30378,10 +30378,10 @@
         <v>0</v>
       </c>
       <c r="Y232" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z232" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA232" t="n">
         <v>0</v>
@@ -30427,12 +30427,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30468,13 +30468,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M233" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -30547,7 +30547,7 @@
         <v>0</v>
       </c>
       <c r="AK233" s="3" t="n">
-        <v>45900.625</v>
+        <v>45900.63541666666</v>
       </c>
     </row>
     <row r="234">
@@ -30685,12 +30685,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>2.55</v>
+        <v>1.39</v>
       </c>
       <c r="M235" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N235" t="n">
-        <v>2.55</v>
+        <v>7.6</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -30765,10 +30765,10 @@
         <v>0</v>
       </c>
       <c r="Y235" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z235" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA235" t="n">
         <v>0</v>
@@ -30805,7 +30805,7 @@
         <v>0</v>
       </c>
       <c r="AK235" s="3" t="n">
-        <v>45900.63541666666</v>
+        <v>45900.64583333334</v>
       </c>
     </row>
     <row r="236">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30855,13 +30855,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -30894,10 +30894,10 @@
         <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z236" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA236" t="n">
         <v>0</v>
@@ -30948,22 +30948,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31410,10 +31410,10 @@
         <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z240" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA240" t="n">
         <v>0</v>
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31500,13 +31500,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31717,27 +31717,27 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31758,13 +31758,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -31797,10 +31797,10 @@
         <v>0</v>
       </c>
       <c r="Y243" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z243" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA243" t="n">
         <v>0</v>
@@ -31837,7 +31837,7 @@
         <v>0</v>
       </c>
       <c r="AK243" s="3" t="n">
-        <v>45900.64583333334</v>
+        <v>45900.65625</v>
       </c>
     </row>
     <row r="244">
@@ -32104,27 +32104,27 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32145,13 +32145,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N246" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -32184,10 +32184,10 @@
         <v>0</v>
       </c>
       <c r="Y246" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z246" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AA246" t="n">
         <v>0</v>
@@ -32224,7 +32224,7 @@
         <v>0</v>
       </c>
       <c r="AK246" s="3" t="n">
-        <v>45900.65625</v>
+        <v>45900.66666666666</v>
       </c>
     </row>
     <row r="247">
@@ -32238,22 +32238,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,22 +32496,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32754,22 +32754,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -32919,13 +32919,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -32964,10 +32964,10 @@
         <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB252" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC252" t="n">
         <v>0</v>
@@ -33012,22 +33012,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33270,22 +33270,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,22 +33399,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,22 +33528,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33657,22 +33657,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,22 +33786,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33822,13 +33822,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -33861,10 +33861,10 @@
         <v>0</v>
       </c>
       <c r="Y259" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z259" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA259" t="n">
         <v>0</v>
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34080,13 +34080,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34125,10 +34125,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB261" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34377,10 +34377,10 @@
         <v>0</v>
       </c>
       <c r="Y263" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z263" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA263" t="n">
         <v>0</v>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34560,22 +34560,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34942,12 +34942,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35062,7 +35062,7 @@
         <v>0</v>
       </c>
       <c r="AK268" s="3" t="n">
-        <v>45900.66666666666</v>
+        <v>45900.67708333334</v>
       </c>
     </row>
     <row r="269">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35200,27 +35200,27 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35320,7 +35320,7 @@
         <v>0</v>
       </c>
       <c r="AK270" s="3" t="n">
-        <v>45900.67708333334</v>
+        <v>45900.6875</v>
       </c>
     </row>
     <row r="271">
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35845,27 +35845,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35965,7 +35965,7 @@
         <v>0</v>
       </c>
       <c r="AK275" s="3" t="n">
-        <v>45900.6875</v>
+        <v>45900.70138888889</v>
       </c>
     </row>
     <row r="276">
@@ -35974,12 +35974,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36094,7 +36094,7 @@
         <v>0</v>
       </c>
       <c r="AK276" s="3" t="n">
-        <v>45900.70138888889</v>
+        <v>45900.70833333334</v>
       </c>
     </row>
     <row r="277">
@@ -36103,12 +36103,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36144,13 +36144,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -36177,16 +36177,16 @@
         <v>0</v>
       </c>
       <c r="W277" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X277" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y277" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Z277" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -36223,7 +36223,7 @@
         <v>0</v>
       </c>
       <c r="AK277" s="3" t="n">
-        <v>45900.70833333334</v>
+        <v>45900.77083333334</v>
       </c>
     </row>
     <row r="278">
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36402,13 +36402,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="M279" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N279" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -36441,10 +36441,10 @@
         <v>2.45</v>
       </c>
       <c r="Y279" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="Z279" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AA279" t="n">
         <v>0</v>
@@ -36490,12 +36490,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36531,13 +36531,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -36564,16 +36564,16 @@
         <v>0</v>
       </c>
       <c r="W280" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X280" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y280" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Z280" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA280" t="n">
         <v>0</v>
@@ -36610,7 +36610,7 @@
         <v>0</v>
       </c>
       <c r="AK280" s="3" t="n">
-        <v>45900.77083333334</v>
+        <v>45900.8125</v>
       </c>
     </row>
     <row r="281">
@@ -36619,12 +36619,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -36634,12 +36634,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36739,7 +36739,7 @@
         <v>0</v>
       </c>
       <c r="AK281" s="3" t="n">
-        <v>45900.8125</v>
+        <v>45900.83333333334</v>
       </c>
     </row>
     <row r="282">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -37006,12 +37006,12 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37047,13 +37047,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M284" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37086,10 +37086,10 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z284" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA284" t="n">
         <v>0</v>
@@ -37126,7 +37126,7 @@
         <v>0</v>
       </c>
       <c r="AK284" s="3" t="n">
-        <v>45900.83333333334</v>
+        <v>45900.85416666666</v>
       </c>
     </row>
     <row r="285">
@@ -37393,12 +37393,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37434,13 +37434,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N287" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -37473,10 +37473,10 @@
         <v>0</v>
       </c>
       <c r="Y287" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z287" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA287" t="n">
         <v>0</v>
@@ -37513,7 +37513,7 @@
         <v>0</v>
       </c>
       <c r="AK287" s="3" t="n">
-        <v>45900.85416666666</v>
+        <v>45900.875</v>
       </c>
     </row>
     <row r="288">
@@ -37656,7 +37656,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37780,7 +37780,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -37795,12 +37795,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37900,7 +37900,7 @@
         <v>0</v>
       </c>
       <c r="AK290" s="3" t="n">
-        <v>45900.875</v>
+        <v>45900.88541666666</v>
       </c>
     </row>
     <row r="291">
@@ -37909,12 +37909,12 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -37924,12 +37924,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38029,7 +38029,7 @@
         <v>0</v>
       </c>
       <c r="AK291" s="3" t="n">
-        <v>45900.88541666666</v>
+        <v>45900.9375</v>
       </c>
     </row>
     <row r="292">
@@ -38038,7 +38038,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -38053,12 +38053,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38158,7 +38158,7 @@
         <v>0</v>
       </c>
       <c r="AK292" s="3" t="n">
-        <v>45900.9375</v>
+        <v>45900.95833333334</v>
       </c>
     </row>
     <row r="293">
@@ -38167,12 +38167,12 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -38182,12 +38182,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38208,13 +38208,13 @@
         </is>
       </c>
       <c r="L293" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M293" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N293" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -38253,10 +38253,10 @@
         <v>0</v>
       </c>
       <c r="AA293" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB293" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC293" t="n">
         <v>0</v>
@@ -38287,135 +38287,6 @@
         <v>0</v>
       </c>
       <c r="AK293" s="3" t="n">
-        <v>45900.95833333334</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="2" t="n">
-        <v>45900</v>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="G294" t="n">
-        <v>0</v>
-      </c>
-      <c r="H294" t="n">
-        <v>0</v>
-      </c>
-      <c r="I294" t="n">
-        <v>0</v>
-      </c>
-      <c r="J294" t="n">
-        <v>0</v>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L294" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M294" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N294" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O294" t="n">
-        <v>0</v>
-      </c>
-      <c r="P294" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
-      <c r="R294" t="n">
-        <v>0</v>
-      </c>
-      <c r="S294" t="n">
-        <v>0</v>
-      </c>
-      <c r="T294" t="n">
-        <v>0</v>
-      </c>
-      <c r="U294" t="n">
-        <v>0</v>
-      </c>
-      <c r="V294" t="n">
-        <v>0</v>
-      </c>
-      <c r="W294" t="n">
-        <v>0</v>
-      </c>
-      <c r="X294" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y294" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA294" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB294" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE294" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF294" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK294" s="3" t="n">
         <v>45900.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-08-31.xlsx
+++ b/jogos_2025-08-31.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.21</v>
+        <v>2.65</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>3.46</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.54</v>
+        <v>1.9</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4922,17 +4922,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5</v>
+        <v>1.69</v>
       </c>
       <c r="M45" t="n">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="N45" t="n">
-        <v>1.57</v>
+        <v>4.06</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6519,10 +6519,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.69</v>
+        <v>2.49</v>
       </c>
       <c r="M49" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="N49" t="n">
-        <v>4.06</v>
+        <v>2.69</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>4.44</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>6.66</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.8</v>
+        <v>1.63</v>
       </c>
       <c r="M65" t="n">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="N65" t="n">
-        <v>2.35</v>
+        <v>5.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9099,10 +9099,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,22 +10179,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,22 +11727,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>10.38</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15807,10 +15807,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16452,10 +16452,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.77</v>
+        <v>3.7</v>
       </c>
       <c r="M131" t="n">
         <v>3.6</v>
       </c>
       <c r="N131" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z131" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -17955,13 +17955,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -17994,10 +17994,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -18048,22 +18048,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,22 +18693,22 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -18897,10 +18897,10 @@
         <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA143" t="n">
         <v>0</v>
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,22 +20241,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,22 +20370,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,22 +20499,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,22 +20628,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,22 +21015,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,22 +21402,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,22 +21531,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21696,13 +21696,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -21735,10 +21735,10 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z165" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA165" t="n">
         <v>0</v>
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z166" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -21993,10 +21993,10 @@
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z167" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA167" t="n">
         <v>0</v>
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22212,13 +22212,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22599,13 +22599,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -22638,16 +22638,16 @@
         <v>0</v>
       </c>
       <c r="Y172" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z172" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,10 +22767,10 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z173" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA173" t="n">
         <v>0</v>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23025,10 +23025,10 @@
         <v>0</v>
       </c>
       <c r="Y175" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z175" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA175" t="n">
         <v>0</v>
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23115,13 +23115,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23244,13 +23244,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23283,16 +23283,16 @@
         <v>0</v>
       </c>
       <c r="Y177" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z177" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA177" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB177" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -23337,22 +23337,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23373,13 +23373,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23595,22 +23595,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,22 +23724,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,22 +23982,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,22 +24111,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,22 +24756,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25566,13 +25566,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -25605,10 +25605,10 @@
         <v>0</v>
       </c>
       <c r="Y195" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z195" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA195" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25695,13 +25695,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -25734,10 +25734,10 @@
         <v>0</v>
       </c>
       <c r="Y196" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z196" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA196" t="n">
         <v>0</v>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,22 +26175,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,22 +26433,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,22 +26562,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26856,13 +26856,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -26895,10 +26895,10 @@
         <v>0</v>
       </c>
       <c r="Y205" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z205" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA205" t="n">
         <v>0</v>
@@ -26949,22 +26949,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,22 +27336,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,22 +27465,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27630,13 +27630,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N211" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -27669,10 +27669,10 @@
         <v>0</v>
       </c>
       <c r="Y211" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z211" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA211" t="n">
         <v>0</v>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,22 +28110,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28239,22 +28239,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,10 +28959,10 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA221" t="n">
         <v>0</v>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29178,13 +29178,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -29217,10 +29217,10 @@
         <v>0</v>
       </c>
       <c r="Y223" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z223" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA223" t="n">
         <v>0</v>
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29307,13 +29307,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -29346,10 +29346,10 @@
         <v>0</v>
       </c>
       <c r="Y224" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z224" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA224" t="n">
         <v>0</v>
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30210,13 +30210,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30249,10 +30249,10 @@
         <v>0</v>
       </c>
       <c r="Y231" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z231" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA231" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30468,13 +30468,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="M233" t="n">
         <v>3.15</v>
       </c>
       <c r="N233" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="M234" t="n">
         <v>3.15</v>
       </c>
       <c r="N234" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30690,22 +30690,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N235" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -30765,10 +30765,10 @@
         <v>0</v>
       </c>
       <c r="Y235" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z235" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA235" t="n">
         <v>0</v>
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30855,13 +30855,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -30894,10 +30894,10 @@
         <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z236" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA236" t="n">
         <v>0</v>
@@ -30948,22 +30948,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -30984,13 +30984,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M237" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N237" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31023,10 +31023,10 @@
         <v>0</v>
       </c>
       <c r="Y237" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z237" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA237" t="n">
         <v>0</v>
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z239" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31758,13 +31758,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="M243" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="N243" t="n">
-        <v>7.1</v>
+        <v>2.5</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -31797,10 +31797,10 @@
         <v>0</v>
       </c>
       <c r="Y243" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="Z243" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AA243" t="n">
         <v>0</v>
@@ -31851,7 +31851,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31887,13 +31887,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M244" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -31926,10 +31926,10 @@
         <v>0</v>
       </c>
       <c r="Y244" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z244" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA244" t="n">
         <v>0</v>
@@ -32109,22 +32109,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,22 +32367,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,22 +32625,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32883,22 +32883,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -32919,13 +32919,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N252" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -32964,10 +32964,10 @@
         <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB252" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC252" t="n">
         <v>0</v>
@@ -33012,22 +33012,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,22 +33141,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33270,22 +33270,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33657,22 +33657,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,22 +34044,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34080,13 +34080,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34119,10 +34119,10 @@
         <v>0</v>
       </c>
       <c r="Y261" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z261" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA261" t="n">
         <v>0</v>
@@ -34302,22 +34302,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34725,13 +34725,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N266" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -34764,10 +34764,10 @@
         <v>0</v>
       </c>
       <c r="Y266" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z266" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA266" t="n">
         <v>0</v>
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34854,13 +34854,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M267" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -34899,10 +34899,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB267" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC267" t="n">
         <v>0</v>
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36144,13 +36144,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="M277" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N277" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -36177,16 +36177,16 @@
         <v>0</v>
       </c>
       <c r="W277" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X277" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y277" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Z277" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36273,13 +36273,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="M278" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N278" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -36306,16 +36306,16 @@
         <v>0</v>
       </c>
       <c r="W278" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X278" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y278" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="Z278" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA278" t="n">
         <v>0</v>
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36402,13 +36402,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M279" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N279" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -36441,10 +36441,10 @@
         <v>2.45</v>
       </c>
       <c r="Y279" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Z279" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AA279" t="n">
         <v>0</v>
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37140,7 +37140,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -37150,12 +37150,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37176,13 +37176,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N285" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -37215,10 +37215,10 @@
         <v>0</v>
       </c>
       <c r="Y285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z285" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA285" t="n">
         <v>0</v>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -37279,12 +37279,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -37305,13 +37305,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -37344,10 +37344,10 @@
         <v>0</v>
       </c>
       <c r="Y286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z286" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA286" t="n">
         <v>0</v>

--- a/jogos_2025-08-31.xlsx
+++ b/jogos_2025-08-31.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.2</v>
+        <v>1.72</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>2.65</v>
       </c>
       <c r="M25" t="n">
         <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>2.55</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.72</v>
+        <v>2.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="Z26" t="n">
         <v>1.78</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.73</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>4.7</v>
+        <v>2.45</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>2.31</v>
+        <v>4.7</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4922,17 +4922,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="N39" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="M41" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="N41" t="n">
-        <v>2.2</v>
+        <v>1.23</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M44" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="N44" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.69</v>
+        <v>5</v>
       </c>
       <c r="M45" t="n">
-        <v>3.74</v>
+        <v>4.5</v>
       </c>
       <c r="N45" t="n">
-        <v>4.06</v>
+        <v>1.57</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>5</v>
+        <v>2.49</v>
       </c>
       <c r="M47" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="N47" t="n">
-        <v>1.57</v>
+        <v>2.69</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.44</v>
+        <v>1.78</v>
       </c>
       <c r="M56" t="n">
-        <v>4.8</v>
+        <v>4.44</v>
       </c>
       <c r="N56" t="n">
-        <v>6.66</v>
+        <v>3.72</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="M57" t="n">
-        <v>4.44</v>
+        <v>4.8</v>
       </c>
       <c r="N57" t="n">
-        <v>3.72</v>
+        <v>6.66</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="N58" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,16 +7932,16 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="M67" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="N67" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,16 +9093,16 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA67" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="M68" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N68" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,16 +9222,16 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB68" t="n">
         <v>1.7</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.65</v>
+        <v>2.65</v>
       </c>
       <c r="M74" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N74" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.8</v>
+        <v>4.15</v>
       </c>
       <c r="M75" t="n">
-        <v>3.65</v>
+        <v>4.32</v>
       </c>
       <c r="N75" t="n">
-        <v>4.4</v>
+        <v>1.71</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,22 +10437,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>6.98</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>10.38</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>10.38</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12840,10 +12840,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15807,10 +15807,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -17955,13 +17955,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -17994,10 +17994,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -18897,10 +18897,10 @@
         <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z143" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA143" t="n">
         <v>0</v>
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,49 +18987,49 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="M144" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N144" t="n">
+        <v>2</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y144" t="n">
         <v>1.85</v>
       </c>
-      <c r="O144" t="n">
-        <v>0</v>
-      </c>
-      <c r="P144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0</v>
-      </c>
-      <c r="S144" t="n">
-        <v>0</v>
-      </c>
-      <c r="T144" t="n">
-        <v>0</v>
-      </c>
-      <c r="U144" t="n">
-        <v>0</v>
-      </c>
-      <c r="V144" t="n">
-        <v>0</v>
-      </c>
-      <c r="W144" t="n">
-        <v>0</v>
-      </c>
-      <c r="X144" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y144" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Z144" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19080,22 +19080,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,22 +19209,22 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,22 +19467,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,22 +19596,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,22 +19725,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20019,13 +20019,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20058,10 +20058,10 @@
         <v>0</v>
       </c>
       <c r="Y152" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z152" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA152" t="n">
         <v>0</v>
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,22 +20241,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,22 +20370,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20664,13 +20664,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -20709,10 +20709,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -20757,22 +20757,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -20922,13 +20922,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -20961,10 +20961,10 @@
         <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z159" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA159" t="n">
         <v>0</v>
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,22 +21273,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,22 +21402,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,22 +21531,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21567,13 +21567,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -21606,10 +21606,10 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA164" t="n">
         <v>0</v>
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21696,13 +21696,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="M165" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N165" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -21735,10 +21735,10 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="Z165" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AA165" t="n">
         <v>0</v>
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,14 +21825,14 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>3.9</v>
+        <v>1.92</v>
       </c>
       <c r="M166" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N166" t="n">
         <v>3.85</v>
       </c>
-      <c r="N166" t="n">
-        <v>1.81</v>
-      </c>
       <c r="O166" t="n">
         <v>0</v>
       </c>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="Z166" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1.63</v>
+        <v>3.9</v>
       </c>
       <c r="M167" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="N167" t="n">
-        <v>4.9</v>
+        <v>1.81</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -21993,10 +21993,10 @@
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z167" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AA167" t="n">
         <v>0</v>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22341,13 +22341,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -22380,10 +22380,10 @@
         <v>0</v>
       </c>
       <c r="Y170" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z170" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA170" t="n">
         <v>0</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22470,13 +22470,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -22509,10 +22509,10 @@
         <v>0</v>
       </c>
       <c r="Y171" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z171" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA171" t="n">
         <v>0</v>
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,10 +22767,10 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z173" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA173" t="n">
         <v>0</v>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22857,13 +22857,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -22896,16 +22896,16 @@
         <v>0</v>
       </c>
       <c r="Y174" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z174" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA174" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23115,13 +23115,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23244,13 +23244,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.37</v>
+        <v>3.7</v>
       </c>
       <c r="M177" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="N177" t="n">
-        <v>7.6</v>
+        <v>2.1</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23283,16 +23283,16 @@
         <v>0</v>
       </c>
       <c r="Y177" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="Z177" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="AA177" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -23337,22 +23337,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23373,13 +23373,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23466,22 +23466,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,22 +23982,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,22 +25143,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25695,13 +25695,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -25734,10 +25734,10 @@
         <v>0</v>
       </c>
       <c r="Y196" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z196" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA196" t="n">
         <v>0</v>
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25824,13 +25824,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -25863,10 +25863,10 @@
         <v>0</v>
       </c>
       <c r="Y197" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z197" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA197" t="n">
         <v>0</v>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,22 +26304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26856,13 +26856,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -26895,10 +26895,10 @@
         <v>0</v>
       </c>
       <c r="Y205" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z205" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA205" t="n">
         <v>0</v>
@@ -26949,22 +26949,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,22 +27078,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,22 +27207,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,22 +27336,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27372,13 +27372,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -27411,10 +27411,10 @@
         <v>0</v>
       </c>
       <c r="Y209" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z209" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA209" t="n">
         <v>0</v>
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28239,22 +28239,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28368,22 +28368,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,22 +28497,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,10 +28959,10 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z221" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA221" t="n">
         <v>0</v>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29307,13 +29307,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -29346,10 +29346,10 @@
         <v>0</v>
       </c>
       <c r="Y224" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z224" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA224" t="n">
         <v>0</v>
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29565,13 +29565,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -29604,10 +29604,10 @@
         <v>0</v>
       </c>
       <c r="Y226" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z226" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA226" t="n">
         <v>0</v>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M228" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -29862,10 +29862,10 @@
         <v>0</v>
       </c>
       <c r="Y228" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z228" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA228" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30210,13 +30210,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30249,10 +30249,10 @@
         <v>0</v>
       </c>
       <c r="Y231" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z231" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA231" t="n">
         <v>0</v>
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30690,22 +30690,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,22 +30948,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -30984,13 +30984,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N237" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31023,10 +31023,10 @@
         <v>0</v>
       </c>
       <c r="Y237" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z237" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA237" t="n">
         <v>0</v>
@@ -31077,22 +31077,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>1.39</v>
+        <v>2.45</v>
       </c>
       <c r="M239" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N239" t="n">
-        <v>7.6</v>
+        <v>3.05</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Z239" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31500,13 +31500,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -31539,10 +31539,10 @@
         <v>0</v>
       </c>
       <c r="Y241" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z241" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA241" t="n">
         <v>0</v>
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -32109,22 +32109,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,22 +32238,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,22 +32367,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,22 +32496,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,22 +32625,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32661,13 +32661,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -32700,10 +32700,10 @@
         <v>0</v>
       </c>
       <c r="Y250" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z250" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA250" t="n">
         <v>0</v>
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32790,13 +32790,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -32835,10 +32835,10 @@
         <v>0</v>
       </c>
       <c r="AA251" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB251" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC251" t="n">
         <v>0</v>
@@ -32883,22 +32883,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33012,7 +33012,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,22 +33141,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33177,13 +33177,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M254" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -33216,10 +33216,10 @@
         <v>0</v>
       </c>
       <c r="Y254" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z254" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA254" t="n">
         <v>0</v>
@@ -33270,22 +33270,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,22 +33399,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,22 +33786,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33822,13 +33822,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N259" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -33861,10 +33861,10 @@
         <v>0</v>
       </c>
       <c r="Y259" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z259" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA259" t="n">
         <v>0</v>
@@ -33915,22 +33915,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34080,13 +34080,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -34119,10 +34119,10 @@
         <v>0</v>
       </c>
       <c r="Y261" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z261" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA261" t="n">
         <v>0</v>
@@ -34173,22 +34173,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34431,22 +34431,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34689,22 +34689,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34854,13 +34854,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N267" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -34899,10 +34899,10 @@
         <v>0</v>
       </c>
       <c r="AA267" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB267" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC267" t="n">
         <v>0</v>
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36273,13 +36273,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M278" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N278" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -36312,10 +36312,10 @@
         <v>2.45</v>
       </c>
       <c r="Y278" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Z278" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AA278" t="n">
         <v>0</v>
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36402,13 +36402,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="M279" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N279" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -36441,10 +36441,10 @@
         <v>2.45</v>
       </c>
       <c r="Y279" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="Z279" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AA279" t="n">
         <v>0</v>
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37047,13 +37047,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>2.47</v>
+        <v>1.59</v>
       </c>
       <c r="M284" t="n">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="N284" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37086,10 +37086,10 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Z284" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AA284" t="n">
         <v>0</v>
@@ -37140,7 +37140,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -37150,12 +37150,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37176,13 +37176,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="M285" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N285" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -37215,10 +37215,10 @@
         <v>0</v>
       </c>
       <c r="Y285" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z285" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA285" t="n">
         <v>0</v>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -37279,12 +37279,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -37305,13 +37305,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -37344,10 +37344,10 @@
         <v>0</v>
       </c>
       <c r="Y286" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z286" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA286" t="n">
         <v>0</v>
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37527,7 +37527,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37656,7 +37656,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G289" t="n">

--- a/jogos_2025-08-31.xlsx
+++ b/jogos_2025-08-31.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="N18" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.72</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.59</v>
+        <v>2.6</v>
       </c>
       <c r="M27" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>1.94</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.5</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>2.55</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
         <v>3.55</v>
       </c>
       <c r="N29" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.35</v>
+        <v>2.21</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N30" t="n">
-        <v>1.97</v>
+        <v>3.46</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.83</v>
+        <v>2.48</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.85</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
         <v>3.55</v>
       </c>
       <c r="N31" t="n">
-        <v>4.3</v>
+        <v>2.55</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4922,17 +4922,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N38" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M39" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="N39" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.1</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="N43" t="n">
-        <v>2.2</v>
+        <v>1.23</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M44" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="N44" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>5</v>
+        <v>1.69</v>
       </c>
       <c r="M45" t="n">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="N45" t="n">
-        <v>1.57</v>
+        <v>4.06</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.83</v>
+        <v>5</v>
       </c>
       <c r="M46" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="N46" t="n">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>2.2</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.49</v>
+        <v>1.83</v>
       </c>
       <c r="M47" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="N47" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.69</v>
+        <v>2.49</v>
       </c>
       <c r="M48" t="n">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="N48" t="n">
-        <v>4.06</v>
+        <v>2.69</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>6.66</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>6.66</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>6.1</v>
       </c>
       <c r="N59" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,16 +8061,16 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.8</v>
+        <v>1.63</v>
       </c>
       <c r="M66" t="n">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="N66" t="n">
-        <v>2.35</v>
+        <v>5.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.65</v>
+        <v>2.04</v>
       </c>
       <c r="M74" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N74" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>3.65</v>
+        <v>1.82</v>
       </c>
       <c r="M79" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N79" t="n">
-        <v>1.97</v>
+        <v>4.3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,22 +11727,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>10.38</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11937,10 +11937,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>6.98</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>10.38</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12840,10 +12840,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15678,10 +15678,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,22 +16758,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,22 +16887,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,22 +17403,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,22 +18048,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18187,12 +18187,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z142" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -18897,10 +18897,10 @@
         <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA143" t="n">
         <v>0</v>
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z144" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19080,22 +19080,22 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,22 +19467,22 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,22 +19596,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,22 +19725,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20019,13 +20019,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20058,10 +20058,10 @@
         <v>0</v>
       </c>
       <c r="Y152" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z152" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA152" t="n">
         <v>0</v>
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,22 +20499,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20664,13 +20664,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -20709,10 +20709,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -20757,22 +20757,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -20922,13 +20922,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -20961,10 +20961,10 @@
         <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z159" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA159" t="n">
         <v>0</v>
@@ -21010,27 +21010,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21051,13 +21051,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21090,10 +21090,10 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z160" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA160" t="n">
         <v>0</v>
@@ -21130,7 +21130,7 @@
         <v>0</v>
       </c>
       <c r="AK160" s="3" t="n">
-        <v>45900.5</v>
+        <v>45900.51041666666</v>
       </c>
     </row>
     <row r="161">
@@ -21139,12 +21139,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21219,10 +21219,10 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z161" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA161" t="n">
         <v>0</v>
@@ -21259,7 +21259,7 @@
         <v>0</v>
       </c>
       <c r="AK161" s="3" t="n">
-        <v>45900.5</v>
+        <v>45900.51041666666</v>
       </c>
     </row>
     <row r="162">
@@ -21268,27 +21268,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21309,13 +21309,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21348,10 +21348,10 @@
         <v>0</v>
       </c>
       <c r="Y162" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z162" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA162" t="n">
         <v>0</v>
@@ -21388,7 +21388,7 @@
         <v>0</v>
       </c>
       <c r="AK162" s="3" t="n">
-        <v>45900.5</v>
+        <v>45900.51041666666</v>
       </c>
     </row>
     <row r="163">
@@ -21397,27 +21397,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21517,7 +21517,7 @@
         <v>0</v>
       </c>
       <c r="AK163" s="3" t="n">
-        <v>45900.5</v>
+        <v>45900.51736111111</v>
       </c>
     </row>
     <row r="164">
@@ -21526,12 +21526,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21567,13 +21567,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1.77</v>
+        <v>3.7</v>
       </c>
       <c r="M164" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N164" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -21606,10 +21606,10 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="Z164" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AA164" t="n">
         <v>0</v>
@@ -21646,7 +21646,7 @@
         <v>0</v>
       </c>
       <c r="AK164" s="3" t="n">
-        <v>45900.5</v>
+        <v>45900.52083333334</v>
       </c>
     </row>
     <row r="165">
@@ -21655,12 +21655,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21696,13 +21696,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="M165" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="N165" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -21735,16 +21735,16 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z165" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AA165" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB165" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -21775,7 +21775,7 @@
         <v>0</v>
       </c>
       <c r="AK165" s="3" t="n">
-        <v>45900.51041666666</v>
+        <v>45900.52083333334</v>
       </c>
     </row>
     <row r="166">
@@ -21784,12 +21784,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z166" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -21904,7 +21904,7 @@
         <v>0</v>
       </c>
       <c r="AK166" s="3" t="n">
-        <v>45900.51041666666</v>
+        <v>45900.52083333334</v>
       </c>
     </row>
     <row r="167">
@@ -21913,12 +21913,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="M167" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="N167" t="n">
-        <v>1.81</v>
+        <v>3.45</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -21993,10 +21993,10 @@
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="Z167" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AA167" t="n">
         <v>0</v>
@@ -22033,7 +22033,7 @@
         <v>0</v>
       </c>
       <c r="AK167" s="3" t="n">
-        <v>45900.51041666666</v>
+        <v>45900.52083333334</v>
       </c>
     </row>
     <row r="168">
@@ -22042,27 +22042,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22162,7 +22162,7 @@
         <v>0</v>
       </c>
       <c r="AK168" s="3" t="n">
-        <v>45900.51736111111</v>
+        <v>45900.52083333334</v>
       </c>
     </row>
     <row r="169">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22341,13 +22341,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="M170" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N170" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -22380,10 +22380,10 @@
         <v>0</v>
       </c>
       <c r="Y170" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z170" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA170" t="n">
         <v>0</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22687,12 +22687,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22807,7 +22807,7 @@
         <v>0</v>
       </c>
       <c r="AK173" s="3" t="n">
-        <v>45900.52083333334</v>
+        <v>45900.54166666666</v>
       </c>
     </row>
     <row r="174">
@@ -22816,12 +22816,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22857,13 +22857,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -22896,16 +22896,16 @@
         <v>0</v>
       </c>
       <c r="Y174" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z174" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -22936,7 +22936,7 @@
         <v>0</v>
       </c>
       <c r="AK174" s="3" t="n">
-        <v>45900.52083333334</v>
+        <v>45900.54166666666</v>
       </c>
     </row>
     <row r="175">
@@ -22945,12 +22945,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23065,7 +23065,7 @@
         <v>0</v>
       </c>
       <c r="AK175" s="3" t="n">
-        <v>45900.52083333334</v>
+        <v>45900.54166666666</v>
       </c>
     </row>
     <row r="176">
@@ -23074,12 +23074,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23194,7 +23194,7 @@
         <v>0</v>
       </c>
       <c r="AK176" s="3" t="n">
-        <v>45900.52083333334</v>
+        <v>45900.54166666666</v>
       </c>
     </row>
     <row r="177">
@@ -23203,12 +23203,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23244,13 +23244,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23283,10 +23283,10 @@
         <v>0</v>
       </c>
       <c r="Y177" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z177" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA177" t="n">
         <v>0</v>
@@ -23323,7 +23323,7 @@
         <v>0</v>
       </c>
       <c r="AK177" s="3" t="n">
-        <v>45900.52083333334</v>
+        <v>45900.54166666666</v>
       </c>
     </row>
     <row r="178">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
+          <t>Harju Jalgpallikool</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
           <t>Tammeka</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,22 +23595,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24147,13 +24147,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24405,13 +24405,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,22 +25143,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25566,13 +25566,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N195" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -25605,10 +25605,10 @@
         <v>0</v>
       </c>
       <c r="Y195" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z195" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA195" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25695,13 +25695,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -25734,10 +25734,10 @@
         <v>0</v>
       </c>
       <c r="Y196" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z196" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA196" t="n">
         <v>0</v>
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25824,13 +25824,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -25863,10 +25863,10 @@
         <v>0</v>
       </c>
       <c r="Y197" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z197" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA197" t="n">
         <v>0</v>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -25953,13 +25953,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -25992,10 +25992,10 @@
         <v>0</v>
       </c>
       <c r="Y198" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z198" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA198" t="n">
         <v>0</v>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,22 +26304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26340,13 +26340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26379,10 +26379,10 @@
         <v>0</v>
       </c>
       <c r="Y201" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z201" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA201" t="n">
         <v>0</v>
@@ -26433,22 +26433,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,22 +26562,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,7 +26691,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,22 +27078,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,22 +27207,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27372,13 +27372,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -27411,10 +27411,10 @@
         <v>0</v>
       </c>
       <c r="Y209" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z209" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA209" t="n">
         <v>0</v>
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,22 +27852,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29565,13 +29565,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -29604,10 +29604,10 @@
         <v>0</v>
       </c>
       <c r="Y226" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z226" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA226" t="n">
         <v>0</v>
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N228" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -29862,10 +29862,10 @@
         <v>0</v>
       </c>
       <c r="Y228" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z228" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA228" t="n">
         <v>0</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -29952,13 +29952,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -29991,10 +29991,10 @@
         <v>0</v>
       </c>
       <c r="Y229" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z229" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA229" t="n">
         <v>0</v>
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30468,13 +30468,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="M233" t="n">
         <v>3.15</v>
       </c>
       <c r="N233" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="M234" t="n">
         <v>3.15</v>
       </c>
       <c r="N234" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -30765,10 +30765,10 @@
         <v>0</v>
       </c>
       <c r="Y235" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z235" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA235" t="n">
         <v>0</v>
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,22 +30948,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,22 +31077,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>2.45</v>
+        <v>1.39</v>
       </c>
       <c r="M239" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N239" t="n">
-        <v>3.05</v>
+        <v>7.6</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Z239" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,22 +31464,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31500,13 +31500,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -31539,10 +31539,10 @@
         <v>0</v>
       </c>
       <c r="Y241" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z241" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA241" t="n">
         <v>0</v>
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31887,13 +31887,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="M244" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="N244" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -31926,10 +31926,10 @@
         <v>0</v>
       </c>
       <c r="Y244" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="Z244" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AA244" t="n">
         <v>0</v>
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32016,13 +32016,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="M245" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="N245" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -32055,10 +32055,10 @@
         <v>0</v>
       </c>
       <c r="Y245" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="Z245" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AA245" t="n">
         <v>0</v>
@@ -32109,22 +32109,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32661,13 +32661,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -32700,10 +32700,10 @@
         <v>0</v>
       </c>
       <c r="Y250" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z250" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA250" t="n">
         <v>0</v>
@@ -32754,22 +32754,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32790,13 +32790,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N251" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -32835,10 +32835,10 @@
         <v>0</v>
       </c>
       <c r="AA251" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB251" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC251" t="n">
         <v>0</v>
@@ -32883,22 +32883,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33177,13 +33177,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -33216,10 +33216,10 @@
         <v>0</v>
       </c>
       <c r="Y254" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z254" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA254" t="n">
         <v>0</v>
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,22 +33399,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,22 +34044,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34383,10 +34383,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB263" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -34560,7 +34560,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34596,13 +34596,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M265" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -34635,10 +34635,10 @@
         <v>0</v>
       </c>
       <c r="Y265" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z265" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA265" t="n">
         <v>0</v>
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34818,22 +34818,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34854,13 +34854,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M267" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -34893,10 +34893,10 @@
         <v>0</v>
       </c>
       <c r="Y267" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z267" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA267" t="n">
         <v>0</v>
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36144,13 +36144,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="M277" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N277" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -36177,16 +36177,16 @@
         <v>0</v>
       </c>
       <c r="W277" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X277" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y277" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Z277" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36273,13 +36273,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="M278" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N278" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -36306,16 +36306,16 @@
         <v>0</v>
       </c>
       <c r="W278" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X278" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Y278" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Z278" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AA278" t="n">
         <v>0</v>
@@ -36634,12 +36634,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37527,7 +37527,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37656,7 +37656,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G289" t="n">

--- a/jogos_2025-08-31.xlsx
+++ b/jogos_2025-08-31.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Manly United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sutherland Sharks</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Manly United</t>
+          <t>Sutherland Sharks</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nagoya Grampus</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.85</v>
+        <v>3.46</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.03</v>
+        <v>2.48</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jubilo Iwata</t>
+          <t>Machida Zelvia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cerezo Osaka</t>
+          <t>Kashiwa Reysol</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sanfrecce Hiroshima</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
         <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Shonan Bellmare</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Machida Zelvia</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Cerezo Osaka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Sanfrecce Hiroshima</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Jubilo Iwata</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kashiwa Reysol</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="M29" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>4.3</v>
+        <v>2.31</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shonan Bellmare</t>
+          <t>Nagoya Grampus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="M31" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="N39" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="M44" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="N44" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>5</v>
+        <v>2.49</v>
       </c>
       <c r="M46" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="N46" t="n">
-        <v>1.57</v>
+        <v>2.69</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="M47" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N47" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.49</v>
+        <v>1.83</v>
       </c>
       <c r="M48" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="N48" t="n">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6777,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>6.66</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7422,10 +7422,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="M56" t="n">
-        <v>4.44</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>3.72</v>
+        <v>5</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="M59" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="N59" t="n">
-        <v>12</v>
+        <v>6.66</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,16 +8061,16 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>4.44</v>
       </c>
       <c r="N60" t="n">
-        <v>5</v>
+        <v>3.72</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.8</v>
+        <v>1.63</v>
       </c>
       <c r="M65" t="n">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="N65" t="n">
-        <v>2.35</v>
+        <v>5.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.63</v>
+        <v>2.8</v>
       </c>
       <c r="M66" t="n">
-        <v>3.98</v>
+        <v>3.7</v>
       </c>
       <c r="N66" t="n">
-        <v>5.3</v>
+        <v>2.35</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.65</v>
+        <v>1.82</v>
       </c>
       <c r="M71" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>1.97</v>
+        <v>4.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.65</v>
+        <v>4.15</v>
       </c>
       <c r="M73" t="n">
-        <v>3.2</v>
+        <v>4.32</v>
       </c>
       <c r="N73" t="n">
-        <v>2.75</v>
+        <v>1.71</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.04</v>
+        <v>5.73</v>
       </c>
       <c r="M74" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="N74" t="n">
-        <v>3.45</v>
+        <v>1.62</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10179,22 +10179,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="M77" t="n">
-        <v>4.32</v>
+        <v>3.45</v>
       </c>
       <c r="N77" t="n">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,22 +10437,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.82</v>
+        <v>2.65</v>
       </c>
       <c r="M79" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N79" t="n">
-        <v>4.3</v>
+        <v>2.75</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="M81" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N81" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>6.98</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>10.38</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11937,10 +11937,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>5.78</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>10.38</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12969,10 +12969,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>5.78</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Inter Turku</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14259,10 +14259,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="M109" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="N109" t="n">
-        <v>7.1</v>
+        <v>3.4</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,16 +14511,16 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15678,10 +15678,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ružomberok</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,22 +16758,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Rheindorf Altach</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17355,10 +17355,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -17403,22 +17403,22 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rheindorf Altach</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17661,22 +17661,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,22 +18048,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>SD Tarazona</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,22 +18177,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18342,13 +18342,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18381,10 +18381,10 @@
         <v>0</v>
       </c>
       <c r="Y139" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z139" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA139" t="n">
         <v>0</v>
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19374,13 +19374,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19413,10 +19413,10 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z147" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA147" t="n">
         <v>0</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,22 +19725,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SD Tarazona</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,22 +19854,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,22 +20112,22 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,22 +20370,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Ružomberok</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21696,13 +21696,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="M165" t="n">
-        <v>5.3</v>
+        <v>3.85</v>
       </c>
       <c r="N165" t="n">
-        <v>7.6</v>
+        <v>4.3</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -21735,16 +21735,16 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="Z165" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AA165" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="M167" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="N167" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -21993,10 +21993,10 @@
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="Z167" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AA167" t="n">
         <v>0</v>
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22212,13 +22212,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22251,16 +22251,16 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z169" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22341,13 +22341,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="M170" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N170" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -22380,10 +22380,10 @@
         <v>0</v>
       </c>
       <c r="Y170" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z170" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA170" t="n">
         <v>0</v>
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>7.03</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23115,13 +23115,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,22 +23337,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,22 +23466,22 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,22 +23595,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,22 +24111,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24147,13 +24147,13 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24405,13 +24405,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,22 +24627,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24663,13 +24663,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25050,13 +25050,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -25143,22 +25143,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -26046,22 +26046,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26340,13 +26340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -26379,10 +26379,10 @@
         <v>0</v>
       </c>
       <c r="Y201" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z201" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA201" t="n">
         <v>0</v>
@@ -26562,22 +26562,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26598,13 +26598,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -26643,10 +26643,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB203" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,22 +27336,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>APOEL</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>APOEL</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,22 +27852,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27888,13 +27888,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -27927,10 +27927,10 @@
         <v>0</v>
       </c>
       <c r="Y213" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z213" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA213" t="n">
         <v>0</v>
@@ -27981,22 +27981,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,22 +28110,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28368,22 +28368,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>KRC Genk</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,22 +28497,22 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>KRC Genk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,10 +28959,10 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA221" t="n">
         <v>0</v>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M222" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="N222" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z222" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29565,13 +29565,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -29604,10 +29604,10 @@
         <v>0</v>
       </c>
       <c r="Y226" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z226" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA226" t="n">
         <v>0</v>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M228" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
@@ -29862,10 +29862,10 @@
         <v>0</v>
       </c>
       <c r="Y228" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z228" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA228" t="n">
         <v>0</v>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -29952,13 +29952,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>1.36</v>
+        <v>3.9</v>
       </c>
       <c r="M229" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N229" t="n">
-        <v>7.6</v>
+        <v>1.78</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -29991,10 +29991,10 @@
         <v>0</v>
       </c>
       <c r="Y229" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="Z229" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AA229" t="n">
         <v>0</v>
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30468,13 +30468,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="M233" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N233" t="n">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -30507,10 +30507,10 @@
         <v>0</v>
       </c>
       <c r="Y233" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z233" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA233" t="n">
         <v>0</v>
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="M234" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N234" t="n">
-        <v>2.47</v>
+        <v>2.17</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30636,10 +30636,10 @@
         <v>0</v>
       </c>
       <c r="Y234" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z234" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA234" t="n">
         <v>0</v>
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -31281,10 +31281,10 @@
         <v>0</v>
       </c>
       <c r="Y239" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z239" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA239" t="n">
         <v>0</v>
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M240" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31410,10 +31410,10 @@
         <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z240" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA240" t="n">
         <v>0</v>
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32367,22 +32367,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,22 +32625,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32661,13 +32661,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -32706,10 +32706,10 @@
         <v>0</v>
       </c>
       <c r="AA250" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB250" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC250" t="n">
         <v>0</v>
@@ -32754,22 +32754,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33012,7 +33012,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,22 +33141,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,22 +33399,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33657,22 +33657,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34209,13 +34209,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -34248,10 +34248,10 @@
         <v>0</v>
       </c>
       <c r="Y262" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z262" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA262" t="n">
         <v>0</v>
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34338,13 +34338,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -34383,10 +34383,10 @@
         <v>0</v>
       </c>
       <c r="AA263" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB263" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC263" t="n">
         <v>0</v>
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34596,13 +34596,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N265" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -34635,10 +34635,10 @@
         <v>0</v>
       </c>
       <c r="Y265" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z265" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA265" t="n">
         <v>0</v>
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34854,13 +34854,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>2.25</v>
+        <v>1.39</v>
       </c>
       <c r="M267" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="N267" t="n">
-        <v>3.25</v>
+        <v>7.5</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -34893,10 +34893,10 @@
         <v>0</v>
       </c>
       <c r="Y267" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="Z267" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AA267" t="n">
         <v>0</v>
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35757,13 +35757,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -35796,10 +35796,10 @@
         <v>0</v>
       </c>
       <c r="Y274" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z274" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA274" t="n">
         <v>0</v>
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36144,13 +36144,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="M277" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N277" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -36183,10 +36183,10 @@
         <v>2.45</v>
       </c>
       <c r="Y277" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="Z277" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36402,13 +36402,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="M279" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N279" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -36441,10 +36441,10 @@
         <v>2.45</v>
       </c>
       <c r="Y279" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Z279" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AA279" t="n">
         <v>0</v>
@@ -36634,12 +36634,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37011,7 +37011,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37047,13 +37047,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -37086,10 +37086,10 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z284" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA284" t="n">
         <v>0</v>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -37279,12 +37279,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -37305,13 +37305,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -37344,10 +37344,10 @@
         <v>0</v>
       </c>
       <c r="Y286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z286" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA286" t="n">
         <v>0</v>
@@ -37398,7 +37398,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37656,7 +37656,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G289" t="n">
